--- a/djadmin/iga_20221011.xlsx
+++ b/djadmin/iga_20221011.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="封面" sheetId="1" state="visible" r:id="rId2"/>
@@ -6877,359 +6877,363 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C1:H20"/>
-  <sheetFormatPr defaultColWidth="8.2109375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="8.890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.38"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="8.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="50.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="27.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="39.18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="12" t="s">
+    <row r="1" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
         <v>329</v>
       </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
       <c r="C2" s="53"/>
       <c r="D2" s="53"/>
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-    </row>
-    <row r="3" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="41.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>19</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="47" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="23" t="n">
+    <row r="4" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="n">
         <v>501</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="B4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="C4" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="D4" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H4" s="24"/>
-    </row>
-    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="23" t="n">
+      <c r="E4" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4" s="24"/>
+    </row>
+    <row r="5" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="n">
         <v>503</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="B5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="C5" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="D5" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="G5" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="23" t="n">
+      <c r="E5" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" s="25"/>
+    </row>
+    <row r="6" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="n">
         <v>505</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="B6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="C6" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="D6" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="G6" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="22" t="s">
+      <c r="E6" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="B7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="D7" s="25" t="s">
         <v>334</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="E7" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H7" s="24"/>
-    </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="23" t="n">
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="n">
         <v>511</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="25" t="s">
+      <c r="B8" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="D8" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="G8" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H8" s="24"/>
-    </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="23" t="n">
+      <c r="E8" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" s="24"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="n">
         <v>513</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="B9" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="C9" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="D9" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="G9" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H9" s="24"/>
-    </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="28"/>
+      <c r="E9" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" s="24"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="25"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="22" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
         <v>336</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="28" t="s">
+      <c r="B11" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="D11" s="25" t="s">
         <v>337</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="E11" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="22" t="s">
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" customFormat="false" ht="90.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="28" t="s">
+      <c r="B12" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="D12" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="E12" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H12" s="25"/>
-    </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="23" t="n">
+      <c r="F12" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="n">
         <v>510</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="28" t="s">
+      <c r="B13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="D13" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="G13" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="23" t="n">
+      <c r="E13" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="n">
         <v>512</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="B14" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="23" t="n">
+        <v>26</v>
+      </c>
       <c r="F14" s="25"/>
-      <c r="G14" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="23" t="n">
+    </row>
+    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="n">
         <v>514</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="23" t="s">
+      <c r="B15" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="D15" s="72" t="s">
         <v>339</v>
       </c>
-      <c r="G15" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="23" t="n">
+      <c r="E15" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" s="25"/>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="n">
         <v>516</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="23" t="s">
+      <c r="B16" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="D16" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="G16" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="22" t="s">
+      <c r="E16" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F16" s="25"/>
+    </row>
+    <row r="17" customFormat="false" ht="90.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="28" t="s">
+      <c r="B17" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="D17" s="27" t="s">
         <v>342</v>
       </c>
-      <c r="G17" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="22" t="s">
+      <c r="E17" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F17" s="25"/>
+    </row>
+    <row r="18" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="B18" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="C18" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="F18" s="73" t="s">
+      <c r="D18" s="73" t="s">
         <v>344</v>
       </c>
-      <c r="G18" s="23" t="n">
+      <c r="E18" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H18" s="25"/>
-    </row>
-    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="23" t="n">
+      <c r="F18" s="25"/>
+    </row>
+    <row r="19" customFormat="false" ht="36.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="n">
         <v>526</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="B19" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="C19" s="28" t="s">
         <v>54</v>
       </c>
+      <c r="D19" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>345</v>
+      </c>
       <c r="F19" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="H19" s="25" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="29" t="s">
+    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="52" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="D20" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="E20" s="29" t="s">
         <v>281</v>
       </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
